--- a/docentes/Muñoz Rivadeneyra Salvador - Estadisticos 20212.xlsx
+++ b/docentes/Muñoz Rivadeneyra Salvador - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="22">
   <si>
     <t>Mat</t>
   </si>
@@ -76,73 +76,13 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>CONGUILLO</t>
-  </si>
-  <si>
-    <t>CUATRA</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>OLTEHUA</t>
-  </si>
-  <si>
-    <t>PACHECO</t>
-  </si>
-  <si>
-    <t>TIBURCIO</t>
-  </si>
-  <si>
-    <t>ZOPIYACTLE</t>
-  </si>
-  <si>
-    <t>JUAREZ</t>
-  </si>
-  <si>
-    <t>REYNOSO</t>
-  </si>
-  <si>
-    <t>MAZAHUA</t>
-  </si>
-  <si>
-    <t>ORTEGA</t>
-  </si>
-  <si>
-    <t>CONSUELO DALILA</t>
-  </si>
-  <si>
-    <t>MARIA</t>
-  </si>
-  <si>
-    <t>EMELIN JIROMI</t>
-  </si>
-  <si>
-    <t>AIDA</t>
-  </si>
-  <si>
-    <t>ODALYS</t>
-  </si>
-  <si>
-    <t>VALERIA</t>
-  </si>
-  <si>
-    <t>SANDY SAMARA</t>
-  </si>
-  <si>
-    <t>TAILY</t>
-  </si>
-  <si>
-    <t>DIANA VIANNEY</t>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>JOSSELIN ANDREA</t>
   </si>
 </sst>
 </file>
@@ -543,16 +483,19 @@
         <v>31</v>
       </c>
       <c r="D2">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>93.55</v>
+      </c>
+      <c r="H2">
+        <v>7.1</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -566,16 +509,19 @@
         <v>28</v>
       </c>
       <c r="D3">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>82.14</v>
+      </c>
+      <c r="H3">
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -589,16 +535,19 @@
         <v>34</v>
       </c>
       <c r="D4">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>82.34999999999999</v>
+      </c>
+      <c r="H4">
+        <v>8.5</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -612,16 +561,19 @@
         <v>19</v>
       </c>
       <c r="D5">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>73.68000000000001</v>
+      </c>
+      <c r="H5">
+        <v>8.4</v>
       </c>
     </row>
   </sheetData>
@@ -677,7 +629,7 @@
         <v>31</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -700,7 +652,7 @@
         <v>28</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -723,7 +675,7 @@
         <v>34</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -746,7 +698,7 @@
         <v>19</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="F5">
         <v>0</v>
@@ -805,16 +757,19 @@
         <v>31</v>
       </c>
       <c r="D2">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>93.55</v>
+      </c>
+      <c r="H2">
+        <v>7.1</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -828,16 +783,19 @@
         <v>28</v>
       </c>
       <c r="D3">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>82.14</v>
+      </c>
+      <c r="H3">
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -851,16 +809,19 @@
         <v>34</v>
       </c>
       <c r="D4">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>82.34999999999999</v>
+      </c>
+      <c r="H4">
+        <v>8.5</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -874,16 +835,19 @@
         <v>19</v>
       </c>
       <c r="D5">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>73.68000000000001</v>
+      </c>
+      <c r="H5">
+        <v>8.4</v>
       </c>
     </row>
   </sheetData>
@@ -893,7 +857,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -925,208 +889,24 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920118</v>
+        <v>19330051920177</v>
       </c>
       <c r="B2" t="s">
         <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D2" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>20330051920121</v>
-      </c>
-      <c r="B3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D3" t="s">
-        <v>34</v>
-      </c>
-      <c r="E3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>20330051920123</v>
-      </c>
-      <c r="B4" t="s">
-        <v>21</v>
-      </c>
-      <c r="C4" t="s">
-        <v>29</v>
-      </c>
-      <c r="D4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>20330051920125</v>
-      </c>
-      <c r="B5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D5" t="s">
-        <v>36</v>
-      </c>
-      <c r="E5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" t="s">
-        <v>11</v>
-      </c>
-      <c r="G5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>20330051920127</v>
-      </c>
-      <c r="B6" t="s">
-        <v>23</v>
-      </c>
-      <c r="C6" t="s">
-        <v>23</v>
-      </c>
-      <c r="D6" t="s">
-        <v>37</v>
-      </c>
-      <c r="E6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" t="s">
-        <v>11</v>
-      </c>
-      <c r="G6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>20330051920139</v>
-      </c>
-      <c r="B7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D7" t="s">
-        <v>38</v>
-      </c>
-      <c r="E7" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" t="s">
-        <v>11</v>
-      </c>
-      <c r="G7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>19330051920387</v>
-      </c>
-      <c r="B8" t="s">
-        <v>25</v>
-      </c>
-      <c r="C8" t="s">
-        <v>21</v>
-      </c>
-      <c r="D8" t="s">
-        <v>39</v>
-      </c>
-      <c r="E8" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" t="s">
-        <v>11</v>
-      </c>
-      <c r="G8">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>20330051920389</v>
-      </c>
-      <c r="B9" t="s">
-        <v>26</v>
-      </c>
-      <c r="C9" t="s">
-        <v>31</v>
-      </c>
-      <c r="D9" t="s">
-        <v>40</v>
-      </c>
-      <c r="E9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" t="s">
-        <v>11</v>
-      </c>
-      <c r="G9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>20330051920150</v>
-      </c>
-      <c r="B10" t="s">
-        <v>27</v>
-      </c>
-      <c r="C10" t="s">
-        <v>32</v>
-      </c>
-      <c r="D10" t="s">
-        <v>41</v>
-      </c>
-      <c r="E10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" t="s">
-        <v>11</v>
-      </c>
-      <c r="G10">
         <v>2</v>
       </c>
     </row>

--- a/docentes/Muñoz Rivadeneyra Salvador - Estadisticos 20212.xlsx
+++ b/docentes/Muñoz Rivadeneyra Salvador - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="31">
   <si>
     <t>Mat</t>
   </si>
@@ -76,13 +76,40 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
     <t>SANCHEZ</t>
   </si>
   <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
+    <t>RUIZ</t>
+  </si>
+  <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
     <t>MARTINEZ</t>
   </si>
   <si>
+    <t>APARICIO</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>ITZEL</t>
+  </si>
+  <si>
     <t>JOSSELIN ANDREA</t>
+  </si>
+  <si>
+    <t>YAZMIN</t>
+  </si>
+  <si>
+    <t>XIMENA MICHELL</t>
   </si>
 </sst>
 </file>
@@ -857,7 +884,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -889,16 +916,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>19330051920177</v>
+        <v>20330051920202</v>
       </c>
       <c r="B2" t="s">
         <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D2" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -907,6 +934,75 @@
         <v>10</v>
       </c>
       <c r="G2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3">
+        <v>19330051920177</v>
+      </c>
+      <c r="B3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>20330051920129</v>
+      </c>
+      <c r="B4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>20330051920145</v>
+      </c>
+      <c r="B5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D5" t="s">
+        <v>30</v>
+      </c>
+      <c r="E5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G5">
         <v>2</v>
       </c>
     </row>

--- a/docentes/Muñoz Rivadeneyra Salvador - Estadisticos 20212.xlsx
+++ b/docentes/Muñoz Rivadeneyra Salvador - Estadisticos 20212.xlsx
@@ -957,7 +957,7 @@
         <v>10</v>
       </c>
       <c r="G3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -980,7 +980,7 @@
         <v>11</v>
       </c>
       <c r="G4">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -1003,7 +1003,7 @@
         <v>11</v>
       </c>
       <c r="G5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Muñoz Rivadeneyra Salvador - Estadisticos 20212.xlsx
+++ b/docentes/Muñoz Rivadeneyra Salvador - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="30">
   <si>
     <t>Mat</t>
   </si>
@@ -76,12 +76,12 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
     <t>DE JESUS</t>
   </si>
   <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
     <t>JIMENEZ</t>
   </si>
   <si>
@@ -91,19 +91,16 @@
     <t>CASTILLO</t>
   </si>
   <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
     <t>APARICIO</t>
   </si>
   <si>
     <t>LOPEZ</t>
   </si>
   <si>
+    <t>JESUS URIEL</t>
+  </si>
+  <si>
     <t>ITZEL</t>
-  </si>
-  <si>
-    <t>JOSSELIN ANDREA</t>
   </si>
   <si>
     <t>YAZMIN</t>
@@ -533,22 +530,22 @@
         <v>10</v>
       </c>
       <c r="C3">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G3">
-        <v>82.14</v>
+        <v>82.76000000000001</v>
       </c>
       <c r="H3">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -562,19 +559,19 @@
         <v>34</v>
       </c>
       <c r="D4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G4">
-        <v>82.34999999999999</v>
+        <v>85.29000000000001</v>
       </c>
       <c r="H4">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -673,13 +670,13 @@
         <v>10</v>
       </c>
       <c r="C3">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D3">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E3">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -702,7 +699,7 @@
         <v>34</v>
       </c>
       <c r="E4">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -807,22 +804,22 @@
         <v>10</v>
       </c>
       <c r="C3">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G3">
-        <v>82.14</v>
+        <v>82.76000000000001</v>
       </c>
       <c r="H3">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -836,19 +833,19 @@
         <v>34</v>
       </c>
       <c r="D4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G4">
-        <v>82.34999999999999</v>
+        <v>85.29000000000001</v>
       </c>
       <c r="H4">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -916,16 +913,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920202</v>
+        <v>20330051920259</v>
       </c>
       <c r="B2" t="s">
         <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -939,16 +936,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>19330051920177</v>
+        <v>20330051920202</v>
       </c>
       <c r="B3" t="s">
         <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -968,10 +965,10 @@
         <v>21</v>
       </c>
       <c r="C4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -991,10 +988,10 @@
         <v>22</v>
       </c>
       <c r="C5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>

--- a/docentes/Muñoz Rivadeneyra Salvador - Estadisticos 20212.xlsx
+++ b/docentes/Muñoz Rivadeneyra Salvador - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="33">
   <si>
     <t>Mat</t>
   </si>
@@ -76,37 +76,46 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>ROBLES</t>
+  </si>
+  <si>
+    <t>SILVESTRE</t>
+  </si>
+  <si>
+    <t>RUIZ</t>
+  </si>
+  <si>
     <t>XOTLANIHUA</t>
   </si>
   <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
     <t>JIMENEZ</t>
   </si>
   <si>
-    <t>RUIZ</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
+    <t>IXMATLAHUA</t>
+  </si>
+  <si>
+    <t>ARIAS</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
   </si>
   <si>
     <t>APARICIO</t>
   </si>
   <si>
-    <t>LOPEZ</t>
+    <t>ALAN URIEL</t>
+  </si>
+  <si>
+    <t>YAIR</t>
+  </si>
+  <si>
+    <t>XIMENA MICHELL</t>
   </si>
   <si>
     <t>JESUS URIEL</t>
   </si>
   <si>
-    <t>ITZEL</t>
-  </si>
-  <si>
     <t>YAZMIN</t>
-  </si>
-  <si>
-    <t>XIMENA MICHELL</t>
   </si>
 </sst>
 </file>
@@ -507,10 +516,10 @@
         <v>31</v>
       </c>
       <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
         <v>2</v>
-      </c>
-      <c r="E2">
-        <v>0</v>
       </c>
       <c r="F2">
         <v>29</v>
@@ -519,7 +528,7 @@
         <v>93.55</v>
       </c>
       <c r="H2">
-        <v>7.1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -533,19 +542,19 @@
         <v>29</v>
       </c>
       <c r="D3">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F3">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G3">
-        <v>82.76000000000001</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="H3">
-        <v>8.6</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -559,19 +568,19 @@
         <v>34</v>
       </c>
       <c r="D4">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F4">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G4">
-        <v>85.29000000000001</v>
+        <v>91.18000000000001</v>
       </c>
       <c r="H4">
-        <v>8.6</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -585,19 +594,19 @@
         <v>19</v>
       </c>
       <c r="D5">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="G5">
-        <v>73.68000000000001</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="H5">
-        <v>8.4</v>
+        <v>7.7</v>
       </c>
     </row>
   </sheetData>
@@ -650,16 +659,19 @@
         <v>31</v>
       </c>
       <c r="D2">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>70.97</v>
+      </c>
+      <c r="H2">
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -673,16 +685,19 @@
         <v>29</v>
       </c>
       <c r="D3">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>93.09999999999999</v>
+      </c>
+      <c r="H3">
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -696,16 +711,19 @@
         <v>34</v>
       </c>
       <c r="D4">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>91.18000000000001</v>
+      </c>
+      <c r="H4">
+        <v>8.1</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -719,16 +737,19 @@
         <v>19</v>
       </c>
       <c r="D5">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>94.73999999999999</v>
+      </c>
+      <c r="H5">
+        <v>7.7</v>
       </c>
     </row>
   </sheetData>
@@ -781,19 +802,19 @@
         <v>31</v>
       </c>
       <c r="D2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F2">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="G2">
-        <v>93.55</v>
+        <v>70.97</v>
       </c>
       <c r="H2">
-        <v>7.1</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -807,19 +828,19 @@
         <v>29</v>
       </c>
       <c r="D3">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F3">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G3">
-        <v>82.76000000000001</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="H3">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -833,19 +854,19 @@
         <v>34</v>
       </c>
       <c r="D4">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F4">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G4">
-        <v>85.29000000000001</v>
+        <v>91.18000000000001</v>
       </c>
       <c r="H4">
-        <v>8.6</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -859,19 +880,19 @@
         <v>19</v>
       </c>
       <c r="D5">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="G5">
-        <v>73.68000000000001</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="H5">
-        <v>8.4</v>
+        <v>8.1</v>
       </c>
     </row>
   </sheetData>
@@ -881,7 +902,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -913,22 +934,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920259</v>
+        <v>20330051920061</v>
       </c>
       <c r="B2" t="s">
         <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -936,39 +957,39 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920202</v>
+        <v>20330051920066</v>
       </c>
       <c r="B3" t="s">
         <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920129</v>
+        <v>20330051920145</v>
       </c>
       <c r="B4" t="s">
         <v>21</v>
       </c>
       <c r="C4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D4" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -977,29 +998,52 @@
         <v>11</v>
       </c>
       <c r="G4">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920145</v>
+        <v>20330051920259</v>
       </c>
       <c r="B5" t="s">
         <v>22</v>
       </c>
       <c r="C5" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>20330051920129</v>
+      </c>
+      <c r="B6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" t="s">
+        <v>27</v>
+      </c>
+      <c r="D6" t="s">
+        <v>32</v>
+      </c>
+      <c r="E6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" t="s">
         <v>11</v>
       </c>
-      <c r="G5">
+      <c r="G6">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Muñoz Rivadeneyra Salvador - Estadisticos 20212.xlsx
+++ b/docentes/Muñoz Rivadeneyra Salvador - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="24">
   <si>
     <t>Mat</t>
   </si>
@@ -76,46 +76,19 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>ROBLES</t>
-  </si>
-  <si>
-    <t>SILVESTRE</t>
-  </si>
-  <si>
-    <t>RUIZ</t>
-  </si>
-  <si>
     <t>XOTLANIHUA</t>
   </si>
   <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>IXMATLAHUA</t>
-  </si>
-  <si>
-    <t>ARIAS</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>APARICIO</t>
-  </si>
-  <si>
-    <t>ALAN URIEL</t>
-  </si>
-  <si>
-    <t>YAIR</t>
-  </si>
-  <si>
-    <t>XIMENA MICHELL</t>
+    <t>SARMIENTO</t>
+  </si>
+  <si>
+    <t>URBINA</t>
   </si>
   <si>
     <t>JESUS URIEL</t>
   </si>
   <si>
-    <t>YAZMIN</t>
+    <t>ALDIR ADALBERTO</t>
   </si>
 </sst>
 </file>
@@ -805,13 +778,13 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F2">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G2">
-        <v>70.97</v>
+        <v>77.42</v>
       </c>
       <c r="H2">
         <v>6.6</v>
@@ -831,16 +804,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F3">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G3">
-        <v>93.09999999999999</v>
+        <v>89.66</v>
       </c>
       <c r="H3">
-        <v>8.199999999999999</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -857,16 +830,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F4">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G4">
-        <v>91.18000000000001</v>
+        <v>97.06</v>
       </c>
       <c r="H4">
-        <v>8.1</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -892,7 +865,7 @@
         <v>94.73999999999999</v>
       </c>
       <c r="H5">
-        <v>8.1</v>
+        <v>7.7</v>
       </c>
     </row>
   </sheetData>
@@ -902,7 +875,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -934,22 +907,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920061</v>
+        <v>20330051920259</v>
       </c>
       <c r="B2" t="s">
         <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="D2" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -957,16 +930,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920066</v>
+        <v>20330051920065</v>
       </c>
       <c r="B3" t="s">
         <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D3" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -975,75 +948,6 @@
         <v>9</v>
       </c>
       <c r="G3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>20330051920145</v>
-      </c>
-      <c r="B4" t="s">
-        <v>21</v>
-      </c>
-      <c r="C4" t="s">
-        <v>26</v>
-      </c>
-      <c r="D4" t="s">
-        <v>30</v>
-      </c>
-      <c r="E4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>20330051920259</v>
-      </c>
-      <c r="B5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C5" t="s">
-        <v>22</v>
-      </c>
-      <c r="D5" t="s">
-        <v>31</v>
-      </c>
-      <c r="E5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" t="s">
-        <v>10</v>
-      </c>
-      <c r="G5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>20330051920129</v>
-      </c>
-      <c r="B6" t="s">
-        <v>23</v>
-      </c>
-      <c r="C6" t="s">
-        <v>27</v>
-      </c>
-      <c r="D6" t="s">
-        <v>32</v>
-      </c>
-      <c r="E6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" t="s">
-        <v>11</v>
-      </c>
-      <c r="G6">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Muñoz Rivadeneyra Salvador - Estadisticos 20212.xlsx
+++ b/docentes/Muñoz Rivadeneyra Salvador - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="30">
   <si>
     <t>Mat</t>
   </si>
@@ -76,16 +76,34 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>ZGAIP</t>
+  </si>
+  <si>
     <t>XOTLANIHUA</t>
   </si>
   <si>
+    <t>FLORES</t>
+  </si>
+  <si>
     <t>SARMIENTO</t>
   </si>
   <si>
+    <t>OJEDA</t>
+  </si>
+  <si>
+    <t>CERVANTES</t>
+  </si>
+  <si>
     <t>URBINA</t>
   </si>
   <si>
+    <t>YAEL</t>
+  </si>
+  <si>
     <t>JESUS URIEL</t>
+  </si>
+  <si>
+    <t>JAVIER</t>
   </si>
   <si>
     <t>ALDIR ADALBERTO</t>
@@ -875,7 +893,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -907,22 +925,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920259</v>
+        <v>20330051920386</v>
       </c>
       <c r="B2" t="s">
         <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D2" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -930,24 +948,70 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920065</v>
+        <v>20330051920259</v>
       </c>
       <c r="B3" t="s">
         <v>20</v>
       </c>
       <c r="C3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>20330051920122</v>
+      </c>
+      <c r="B4" t="s">
         <v>21</v>
       </c>
-      <c r="D3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" t="s">
+      <c r="C4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>20330051920065</v>
+      </c>
+      <c r="B5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D5" t="s">
+        <v>29</v>
+      </c>
+      <c r="E5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" t="s">
         <v>9</v>
       </c>
-      <c r="G3">
+      <c r="G5">
         <v>1</v>
       </c>
     </row>
